--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Thandalacheri_13.374827_80.106079.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Thandalacheri_13.374827_80.106079.xlsx
@@ -722,6 +722,11 @@
           <t>120</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -729,6 +734,11 @@
           <t>121</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -736,6 +746,11 @@
           <t>122</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -743,6 +758,11 @@
           <t>123</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 2D, 3A, 3B, 3C, 3D, 4, 5, 6A, 6B</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -750,6 +770,11 @@
           <t>124</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -757,6 +782,11 @@
           <t>125</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -764,6 +794,11 @@
           <t>126</t>
         </is>
       </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -771,6 +806,11 @@
           <t>127</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B1, 1B2, 1B3, 1B4, 1C, 2</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -778,6 +818,11 @@
           <t>128</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -785,6 +830,11 @@
           <t>129</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3A, 3B, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -792,6 +842,11 @@
           <t>12A</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A, 2B, 2C</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -799,6 +854,11 @@
           <t>12B</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -806,6 +866,11 @@
           <t>13</t>
         </is>
       </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -813,6 +878,11 @@
           <t>130</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 1C, 1D, 1E1, 1E2, 1F, 1G, 1H, 1I1, 1I2, 1J, 1K, 2A, 2B1, 2B2</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -820,6 +890,11 @@
           <t>131</t>
         </is>
       </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -827,6 +902,11 @@
           <t>132</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -834,6 +914,11 @@
           <t>133</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -841,6 +926,11 @@
           <t>134</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 13, 14A, 14B, 15, 16, 17, 18, 19, 2, 20, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -848,6 +938,11 @@
           <t>135</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -855,6 +950,11 @@
           <t>136</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 3, 4, 5, 6, 7A, 7B, 7C, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -862,6 +962,11 @@
           <t>137</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B1, 2B2, 2B3, 2B4, 2B5</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -869,6 +974,11 @@
           <t>138</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 2C, 2D</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -876,6 +986,11 @@
           <t>139</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -883,6 +998,11 @@
           <t>14</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 3</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -890,6 +1010,11 @@
           <t>140</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -897,6 +1022,11 @@
           <t>141</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -904,6 +1034,11 @@
           <t>142</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B1, 2B2</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -911,6 +1046,11 @@
           <t>143</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -918,6 +1058,11 @@
           <t>144</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1, 10, 100, 101, 102, 103, 104, 105, 106, 107, 108, 109, 11, 110, 111, 112, 113, 114, 115, 116, 117, 118, 119, 12, 120, 121, 122, 123, 124, 125, 126, 127, 128, 129, 13, 130, 131, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 4, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 5, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 6, 60, 61, 62, 63, 64, 65, 66, 67, 68, 69, 7, 70, 71, 72, 73, 74, 75, 76, 77, 78, 79, 8, 80, 81, 82, 83, 84, 85, 86, 87, 88, 89, 9, 90, 91, 92, 93, 94, 95, 96, 97, 98, 99</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -925,6 +1070,11 @@
           <t>145</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -932,6 +1082,11 @@
           <t>146</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -939,6 +1094,11 @@
           <t>147</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -946,6 +1106,11 @@
           <t>148</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -953,6 +1118,11 @@
           <t>149</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 2</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -960,6 +1130,11 @@
           <t>15</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>10, 11A, 11B, 12, 13, 1A1, 1A2, 1A3, 1B, 2, 3, 4, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -967,6 +1142,11 @@
           <t>150</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -974,6 +1154,11 @@
           <t>151</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -981,6 +1166,11 @@
           <t>152</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -988,11 +1178,21 @@
           <t>153</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
           <t>154</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Thandalacheri_13.374827_80.106079.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Thandalacheri_13.374827_80.106079.xlsx
@@ -1202,6 +1202,11 @@
           <t>155</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1209,6 +1214,11 @@
           <t>156</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1216,6 +1226,11 @@
           <t>157</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1223,6 +1238,11 @@
           <t>158</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1230,6 +1250,11 @@
           <t>159</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1237,6 +1262,11 @@
           <t>16</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1244,6 +1274,11 @@
           <t>160</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1251,6 +1286,11 @@
           <t>161</t>
         </is>
       </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1258,6 +1298,11 @@
           <t>162</t>
         </is>
       </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 12C, 13, 14A, 14B, 2, 3, 4A, 4B, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1265,6 +1310,11 @@
           <t>163</t>
         </is>
       </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1272,6 +1322,11 @@
           <t>164</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1279,6 +1334,11 @@
           <t>165</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1286,6 +1346,11 @@
           <t>166</t>
         </is>
       </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1293,6 +1358,11 @@
           <t>167</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1300,6 +1370,11 @@
           <t>168</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1307,6 +1382,11 @@
           <t>169</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1314,6 +1394,11 @@
           <t>17</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7A, 7B</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1321,6 +1406,11 @@
           <t>170</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1328,6 +1418,11 @@
           <t>171</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1335,6 +1430,11 @@
           <t>172</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1342,6 +1442,11 @@
           <t>173</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1349,6 +1454,11 @@
           <t>174</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1356,6 +1466,11 @@
           <t>175</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1363,6 +1478,11 @@
           <t>176</t>
         </is>
       </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1370,6 +1490,11 @@
           <t>177</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1377,6 +1502,11 @@
           <t>178</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2A, 2B, 2C</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1384,6 +1514,11 @@
           <t>179</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1391,6 +1526,11 @@
           <t>18</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1398,6 +1538,11 @@
           <t>180</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1405,6 +1550,11 @@
           <t>181</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 2A1, 2A2, 2A3, 2B, 3</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1412,6 +1562,11 @@
           <t>182</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1419,6 +1574,11 @@
           <t>183</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 1C, 2, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1426,6 +1586,11 @@
           <t>184</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 2A, 2B, 3</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1433,6 +1598,11 @@
           <t>185</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C1, 2C2, 2D, 2E1, 2E2, 2F, 2G, 2H, 2I, 2J1, 2J2, 2K1, 2K2, 2L, 2M, 2N, 2O, 2P, 2Q1, 2Q2, 2R, 2S, 2T, 2U</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1440,6 +1610,11 @@
           <t>186</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17A, 17B, 2, 3, 4, 5, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1447,6 +1622,11 @@
           <t>187</t>
         </is>
       </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 3A, 3B, 3C1A, 3C1B, 3C2, 3D, 4A, 4B, 4C, 4D, 4E1, 4E2, 4F1, 4F2, 5A, 5B, 5C1, 5C2, 5D</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1454,6 +1634,11 @@
           <t>188</t>
         </is>
       </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1461,6 +1646,11 @@
           <t>189</t>
         </is>
       </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1468,6 +1658,11 @@
           <t>19</t>
         </is>
       </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1475,6 +1670,11 @@
           <t>190</t>
         </is>
       </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1482,6 +1682,11 @@
           <t>191</t>
         </is>
       </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1489,6 +1694,11 @@
           <t>192</t>
         </is>
       </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1496,6 +1706,11 @@
           <t>193</t>
         </is>
       </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4, 5, 6, 7A, 7B, 8A, 8B</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1503,6 +1718,11 @@
           <t>194</t>
         </is>
       </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1510,6 +1730,11 @@
           <t>195</t>
         </is>
       </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1517,6 +1742,11 @@
           <t>196</t>
         </is>
       </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1524,6 +1754,11 @@
           <t>197</t>
         </is>
       </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1531,6 +1766,11 @@
           <t>198</t>
         </is>
       </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1538,6 +1778,11 @@
           <t>199</t>
         </is>
       </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4, 5A, 5B, 5C</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1545,6 +1790,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>10, 11, 12A, 12B, 13, 14, 15, 16, 1A, 1B, 1C, 1D, 2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1552,6 +1802,11 @@
           <t>20</t>
         </is>
       </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 1C, 2</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1559,6 +1814,11 @@
           <t>200</t>
         </is>
       </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A, 2B, 2C, 3A1A, 3A1B, 3A2, 3B, 4, 5, 6A1A, 6A1B, 6A2, 6B, 7A, 7B</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1566,6 +1826,11 @@
           <t>201</t>
         </is>
       </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1573,6 +1838,11 @@
           <t>202</t>
         </is>
       </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1, 2, 3A1, 3A10, 3A11, 3A12, 3A13, 3A2, 3A3, 3A4, 3A5, 3A6A, 3A6B, 3A7, 3A8, 3A9, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1580,6 +1850,11 @@
           <t>203</t>
         </is>
       </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1587,6 +1862,11 @@
           <t>204</t>
         </is>
       </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 11A, 12A, 12B, 13, 14A, 14B, 2A, 2B, 3, 4A, 4B, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1594,6 +1874,11 @@
           <t>205</t>
         </is>
       </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 3A, 3B, 3C, 4A, 4B, 4C</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1601,6 +1886,11 @@
           <t>206</t>
         </is>
       </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 2A, 2B, 3A, 3B, 3C, 3D, 3E, 3F, 3G</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1608,6 +1898,11 @@
           <t>207</t>
         </is>
       </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C1, 1C2, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1615,6 +1910,11 @@
           <t>208</t>
         </is>
       </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1A1A1A1, 1A1A1B, 1A1B, 1A1C, 1A1D, 1A1E, 1A2A1, 1A2A2, 1A2A3, 1A2B1, 1A2B2, 1B1, 1B2, 2A, 2B, 3A1, 3A2, 3B, 3C, 3D, 3E, 3F, 3G</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1622,6 +1922,11 @@
           <t>209</t>
         </is>
       </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5A, 5B, 5C, 6A, 6B, 6C, 6D, 6E, 7A, 7B, 8A, 8B</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1629,6 +1934,11 @@
           <t>21</t>
         </is>
       </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4A, 4B, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1636,6 +1946,11 @@
           <t>210</t>
         </is>
       </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1643,6 +1958,11 @@
           <t>211</t>
         </is>
       </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 1C, 1D1, 1D2, 2A, 2B, 2C, 2D, 3A, 3B, 3C, 3D, 4, 5, 6A, 6B, 6C, 7A, 7B, 7C, 7D</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1650,6 +1970,11 @@
           <t>212</t>
         </is>
       </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2A, 2B, 3, 4, 5A, 5B, 6A, 6B, 7</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1657,6 +1982,11 @@
           <t>213</t>
         </is>
       </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A, 2B, 3A1A, 3A1B, 3A2, 3B, 3C, 3D, 3E, 3F</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1664,6 +1994,11 @@
           <t>214</t>
         </is>
       </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>1A1A, 1A1B, 1A1C, 1A1D, 1A2, 1B, 1C, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -1671,6 +2006,11 @@
           <t>215</t>
         </is>
       </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A3, 1B, 2A, 2B, 2C, 3A, 3B, 3C, 3D, 3E, 3F, 3G, 3H, 3I, 3J, 3K, 3L, 3M, 3N, 3O, 3P, 3Q, 3R, 3S, 3T, 3U, 3V</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -1678,6 +2018,11 @@
           <t>216</t>
         </is>
       </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -1685,6 +2030,11 @@
           <t>217</t>
         </is>
       </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A, 14B, 15, 16A, 16B, 16C, 17, 18, 19, 20, 2A, 2B, 3, 4A1A, 4A1B, 4A2, 4B, 4C, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -1692,6 +2042,11 @@
           <t>218</t>
         </is>
       </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 10C, 11, 12A, 12B, 13, 14A, 14B, 15A, 15B, 16, 2, 3, 4, 5, 6, 7A1, 7A2, 7B, 8A, 8B, 9A, 9B, 9C</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -1699,6 +2054,11 @@
           <t>219</t>
         </is>
       </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -1706,6 +2066,11 @@
           <t>22</t>
         </is>
       </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2B1, 2B2, 3A, 3B, 4A, 4B, 4C, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -1713,6 +2078,11 @@
           <t>220</t>
         </is>
       </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>10, 11A, 11B, 1A, 1B, 1C, 2A, 2B, 3, 4, 5, 6A, 6B, 6C, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -1720,6 +2090,11 @@
           <t>221</t>
         </is>
       </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 1A, 1B1, 1B2, 2A, 2B, 3A, 3B, 4, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -1727,6 +2102,11 @@
           <t>222</t>
         </is>
       </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -1734,6 +2114,11 @@
           <t>223</t>
         </is>
       </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -1741,6 +2126,11 @@
           <t>224</t>
         </is>
       </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -1748,6 +2138,11 @@
           <t>225</t>
         </is>
       </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -1755,6 +2150,11 @@
           <t>226</t>
         </is>
       </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -1762,6 +2162,11 @@
           <t>227</t>
         </is>
       </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -1769,6 +2174,11 @@
           <t>228</t>
         </is>
       </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -1776,6 +2186,11 @@
           <t>229</t>
         </is>
       </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -1783,6 +2198,11 @@
           <t>23</t>
         </is>
       </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 1C, 2A, 2B, 2C, 2D, 2E, 3A, 3B1, 3B2, 3B3, 3B4, 3B5, 3B6</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -1790,6 +2210,11 @@
           <t>230</t>
         </is>
       </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -1797,6 +2222,11 @@
           <t>231</t>
         </is>
       </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -1804,6 +2234,11 @@
           <t>232</t>
         </is>
       </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B1A, 2B1B, 2B2, 2C, 2D, 2E, 2F, 2G</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -1811,6 +2246,11 @@
           <t>233</t>
         </is>
       </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -1818,6 +2258,11 @@
           <t>234</t>
         </is>
       </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -1825,6 +2270,11 @@
           <t>235</t>
         </is>
       </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -1832,6 +2282,11 @@
           <t>236</t>
         </is>
       </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 1I, 2A, 2B, 2C, 2D</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -1839,6 +2294,11 @@
           <t>237</t>
         </is>
       </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 2C</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -1846,6 +2306,11 @@
           <t>238</t>
         </is>
       </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -1853,6 +2318,11 @@
           <t>239</t>
         </is>
       </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A3, 1A4A, 1A4B, 1B, 1C1, 1C2, 1C3, 1C4, 1D, 1E1A, 1E1B, 1E2, 2A, 2B1, 2B2</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -1860,6 +2330,11 @@
           <t>24</t>
         </is>
       </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 13, 2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -1867,6 +2342,11 @@
           <t>240</t>
         </is>
       </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -1874,6 +2354,11 @@
           <t>241</t>
         </is>
       </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A1A, 2A1B, 2A2, 2B, 2C, 2D1, 2D2, 2E1, 2E2, 2F1, 2F2, 2F3, 2G</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -1881,6 +2366,11 @@
           <t>242</t>
         </is>
       </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B1, 2B10, 2B11, 2B12A, 2B12B, 2B2, 2B3, 2B4A, 2B4B, 2B5, 2B6, 2B7, 2B8, 2B9, 2C, 2D, 2E1, 2E2A, 2E2B1, 2E2B2, 2E3A1A, 2E3A1B, 2E3B, 2E4, 2E5, 2E6, 2E7A, 2E7B, 2E8A1, 2E8A2, 2E8B, 2F, 3A1, 3A2, 3B1, 3B2, 3B3, 3B4, 3B5, 3B6A, 3B6B, 3B7, 3B8, 4A, 4B, 5</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -1888,6 +2378,11 @@
           <t>243</t>
         </is>
       </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>1, 10, 100, 101A, 102, 103, 104A, 104B, 105A, 105B, 106, 107, 108, 109, 11, 110A, 110B, 110C, 111A, 111B, 112, 113, 114, 115, 116, 117A, 117B, 118A, 118B, 119, 12, 120, 121, 123, 124, 125, 126, 127, 128, 129, 13, 130, 131A, 131B, 132, 133A, 133B, 133C, 134, 135, 136, 137, 138, 139, 14, 140, 141, 141A, 142, 143, 144, 145, 146, 147, 148, 149, 15, 151, 152, 153, 154, 155, 156, 157, 16A, 16B, 17, 18, 19, 1O1B, 2, 20, 21, 22, 23, 24, 25, 26A, 26B, 26C, 27A, 27B, 27C, 27D, 28, 29, 3, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 4, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 5, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 6, 60, 61, 62, 63, 64, 65, 66, 67, 68, 69, 70, 71A, 71B, 72A, 72B, 73A1A, 73A1B, 73A2, 73B, 74, 75, 76, 77A, 77B, 78, 79A, 79B, 7A, 7B, 7C, 8, 80A, 80B, 81A1A1, 81A1A2, 81A1B, 81A2, 81B, 82A1, 82A2, 82B, 83A1, 83A1B, 83A2, 83B1, 83B2, 83C, 84, 85, 86A1A, 86A1B, 86A2, 86B, 87, 88, 89, 90, 91, 92A, 92B, 92C, 93A, 93B1, 93B2, 94A, 94B, 95, 96, 97, 98, 99, 9A1, 9A2, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -1895,6 +2390,11 @@
           <t>244</t>
         </is>
       </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -1902,6 +2402,11 @@
           <t>245</t>
         </is>
       </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 5, 6A, 6B, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -1909,6 +2414,11 @@
           <t>246</t>
         </is>
       </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -1916,6 +2426,11 @@
           <t>25</t>
         </is>
       </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>10A, 10B, 11, 12, 13, 14, 15, 16, 17, 18, 1A, 1B, 1C, 1D, 1E, 2A, 2B, 2C, 3A, 3B, 3C, 3D, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -1923,11 +2438,21 @@
           <t>26</t>
         </is>
       </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>10A, 10B, 1A, 1B, 1C, 1D, 2, 3, 4A, 4B1, 4B2, 4B3, 5, 6A, 6B, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
           <t>27</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Thandalacheri_13.374827_80.106079.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Thandalacheri_13.374827_80.106079.xlsx
@@ -2462,6 +2462,11 @@
           <t>28</t>
         </is>
       </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -2469,6 +2474,11 @@
           <t>29</t>
         </is>
       </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6A, 6B, 7A, 7B1, 7B2, 8</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -2476,6 +2486,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -2483,6 +2498,11 @@
           <t>30</t>
         </is>
       </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4A, 4B, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -2490,6 +2510,11 @@
           <t>31</t>
         </is>
       </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -2497,6 +2522,11 @@
           <t>32</t>
         </is>
       </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -2504,6 +2534,11 @@
           <t>33</t>
         </is>
       </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -2511,6 +2546,11 @@
           <t>34</t>
         </is>
       </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -2518,6 +2558,11 @@
           <t>35</t>
         </is>
       </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -2525,6 +2570,11 @@
           <t>36</t>
         </is>
       </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -2532,6 +2582,11 @@
           <t>37</t>
         </is>
       </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -2539,6 +2594,11 @@
           <t>38</t>
         </is>
       </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B1, 2B2, 3A, 3B, 3C, 3D1, 3D2, 3E, 3F, 3G1, 3G2</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -2546,6 +2606,11 @@
           <t>39</t>
         </is>
       </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C1, 1C2, 1C3, 1D, 1E1, 1E2, 1E3, 1F, 1G1, 1G2, 2A, 2B1, 2B2, 2C1, 2C2</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -2553,6 +2618,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 5A, 5B, 6, 7, 8, 9A, 9B1, 9B2</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -2560,6 +2630,11 @@
           <t>40</t>
         </is>
       </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 3, 4, 5A, 5B, 5C, 5D</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -2567,6 +2642,11 @@
           <t>41</t>
         </is>
       </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A, 2B, 2C, 3, 4A, 4B, 4C</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -2574,6 +2654,11 @@
           <t>42</t>
         </is>
       </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -2581,6 +2666,11 @@
           <t>43</t>
         </is>
       </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>1A1A1, 1A1A2, 1A1B, 1A2, 1B1, 1B2, 2A1, 2A2, 2B1, 2B2, 3A, 3B1, 3B2, 3C, 3D1, 3D2, 4</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -2588,6 +2678,11 @@
           <t>44</t>
         </is>
       </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 2D, 2E, 2F, 2G, 2H, 3A, 3B, 3C, 3D, 3E, 3F</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -2595,6 +2690,11 @@
           <t>45</t>
         </is>
       </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 2A, 2B, 2C1, 2C2, 3A1, 3A2, 3B1, 3B2, 4A1, 4A2, 4B1, 4B2</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -2602,6 +2702,11 @@
           <t>46</t>
         </is>
       </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -2609,6 +2714,11 @@
           <t>47</t>
         </is>
       </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -2616,6 +2726,11 @@
           <t>48</t>
         </is>
       </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3A, 3B, 3C</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -2623,6 +2738,11 @@
           <t>49</t>
         </is>
       </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -2630,6 +2750,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 1I, 1J, 2</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -2637,6 +2762,11 @@
           <t>50</t>
         </is>
       </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 1C1, 1C2, 1D, 1E, 2A, 2B, 2C</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -2644,6 +2774,11 @@
           <t>51</t>
         </is>
       </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 3A, 3B, 3C</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -2651,6 +2786,11 @@
           <t>52</t>
         </is>
       </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 2, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -2658,6 +2798,11 @@
           <t>53</t>
         </is>
       </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A3, 1B, 1C, 1D, 1E, 1F, 1G, 2A1, 2A2, 2B, 2C, 2D, 2E, 2F</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -2665,6 +2810,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B1, 1B2, 1C1, 1C2, 1D1, 1D2, 1E1, 1E2, 1F, 2A, 2B, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -2672,6 +2822,11 @@
           <t>55</t>
         </is>
       </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 2C, 2D, 3A, 3B, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -2679,6 +2834,11 @@
           <t>56</t>
         </is>
       </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -2686,6 +2846,11 @@
           <t>57</t>
         </is>
       </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B1, 2B2, 3A1, 3A2, 3B1, 3B2A, 3B2B, 4, 5A, 5B, 6A, 6B</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -2693,6 +2858,11 @@
           <t>58</t>
         </is>
       </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A, 2B, 3A, 3B, 4, 5A, 5B1, 5B2, 5B3, 5C, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -2700,6 +2870,11 @@
           <t>59</t>
         </is>
       </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>10A1, 10A2, 10B, 10C, 10D, 11, 1A, 1B, 2, 3A, 3B, 3C, 4A, 4B, 4C, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -2707,6 +2882,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5A, 5B, 6, 7A1, 7A2, 7B, 7C</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -2714,6 +2894,11 @@
           <t>60</t>
         </is>
       </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4A, 4B, 5A, 5B1, 5B2, 6A, 6B, 6C1, 6C2, 7A, 7B</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -2721,6 +2906,11 @@
           <t>61</t>
         </is>
       </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A, 2B1, 2B2A, 2B2B, 2B2C, 3A, 3B, 4A, 4B, 5A, 5B, 5C, 5D, 5E, 6A1, 6A2, 6B, 6C1A, 6C1B, 6C2</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -2728,6 +2918,11 @@
           <t>62</t>
         </is>
       </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -2735,6 +2930,11 @@
           <t>63</t>
         </is>
       </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2B, 2C, 2D, 2E, 3A1A1A, 3A1A1B, 3A1A2, 3A1A3, 3A1A4, 3A1B, 3A1C, 3A2A, 3A2B, 3B, 4, 5, 6A, 6B1, 6B2, 6C1, 6C2, 6D, 6E, 7A, 7B1, 7B2, 8A, 8B1, 8B2, 9A, 9B, 9C, 9D, 9E, 9F</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -2742,6 +2942,11 @@
           <t>64</t>
         </is>
       </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -2749,6 +2954,11 @@
           <t>65</t>
         </is>
       </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5A, 5B, 6</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -2756,6 +2966,11 @@
           <t>66</t>
         </is>
       </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -2763,6 +2978,11 @@
           <t>67</t>
         </is>
       </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -2770,6 +2990,11 @@
           <t>68</t>
         </is>
       </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>1A1, 1A2A, 1A2B, 1B, 2A1, 2A2, 2B, 2C</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -2777,6 +3002,11 @@
           <t>69</t>
         </is>
       </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -2784,6 +3014,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -2791,6 +3026,11 @@
           <t>70</t>
         </is>
       </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -2798,6 +3038,11 @@
           <t>71</t>
         </is>
       </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4, 5A1, 5A2, 5B, 5C, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -2805,6 +3050,11 @@
           <t>72</t>
         </is>
       </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -2812,6 +3062,11 @@
           <t>73</t>
         </is>
       </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A3, 1B1, 1B2, 2A, 2B, 2C1, 2C2</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -2819,6 +3074,11 @@
           <t>74</t>
         </is>
       </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -2826,6 +3086,11 @@
           <t>75</t>
         </is>
       </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 2A1, 2A2, 2A3, 2A4, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -2833,6 +3098,11 @@
           <t>76</t>
         </is>
       </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 2A1, 2A2, 2B, 3, 4, 5, 6, 7A, 7B, 7C1A, 7C1B, 7C1C, 7C2, 7C3, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -2840,6 +3110,11 @@
           <t>77</t>
         </is>
       </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 12C, 2, 3A, 3B, 4A, 4B, 5, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -2847,6 +3122,11 @@
           <t>78</t>
         </is>
       </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -2854,6 +3134,11 @@
           <t>79</t>
         </is>
       </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -2861,6 +3146,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B1, 2B2, 2C1, 2C2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -2868,6 +3158,11 @@
           <t>80</t>
         </is>
       </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -2875,6 +3170,11 @@
           <t>81</t>
         </is>
       </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>1A1, 1A2A1, 1A2A2, 1A2A3, 1A2B, 1A2C, 1A3, 1B1, 1B2, 1C, 2A, 2B, 3A, 3B, 3C, 3D1, 3D2, 3D3, 3E1, 3E2, 3E3, 3F, 3G, 3H, 3I1, 3I2, 3I3, 3J, 3K, 3L, 3M, 4A, 4B, 5, 6A, 6B, 6C, 7A, 7B1, 7B2A, 7B2B, 7B3, 7B4, 7C, 7D, 7E1, 7E2, 7F1, 7F2A, 7F2B, 7G, 7H, 7I, 7J1, 7J2, 7K1A, 7K1B, 7K2A, 7K2B, 7L1, 7L2, 7M1A1, 7M1A2, 7M1B, 7M2</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -2882,6 +3182,11 @@
           <t>82</t>
         </is>
       </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -2889,6 +3194,11 @@
           <t>83</t>
         </is>
       </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -2896,6 +3206,11 @@
           <t>84</t>
         </is>
       </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -2903,6 +3218,11 @@
           <t>85</t>
         </is>
       </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B1, 1B2, 1C1A, 1C1B, 1C2, 1C3, 1C4, 1C5A, 1C5B, 2A1, 2A2, 2A3, 2A4, 2A5A, 2A5B, 2A6, 2A7, 2B1, 2B2, 2B3, 2B4, 2B5, 2B6, 3</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -2910,6 +3230,11 @@
           <t>86</t>
         </is>
       </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 2D, 2E, 3A, 3B, 3C1, 3C2, 3D, 3E, 3F, 3G, 3H, 3I, 3J, 3K, 3L, 3M, 3N1, 3N2, 3N3, 3O1, 3O2, 3P, 3Q, 3R, 3S, 4A, 4B, 4C, 4D, 4E, 5A, 5B1, 5B2, 5B3</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -2917,6 +3242,11 @@
           <t>87</t>
         </is>
       </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -2924,6 +3254,11 @@
           <t>88</t>
         </is>
       </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>10, 11, 12A, 12B, 13, 14A, 14B, 15A, 15B, 15C, 15D, 16A, 16B1, 16B2, 17, 18, 19, 1A, 20, 2A, 2B1, 2B2, 3A, 3B, 4A, 4B, 5A, 5B, 5C, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -2931,6 +3266,11 @@
           <t>89</t>
         </is>
       </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3A, 3B, 4A, 4B, 5A, 5B, 5C, 6A, 6B, 6C, 6D, 6E, 6F, 6G1, 6G2, 6G3, 6H, 6I, 6J, 7A, 7B, 8A, 8B, 8C1, 8C2, 8C3, 8C4, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -2938,6 +3278,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4, 5, 6A, 6B, 6C, 7</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -2945,6 +3290,11 @@
           <t>90</t>
         </is>
       </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -2952,6 +3302,11 @@
           <t>91</t>
         </is>
       </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A3, 1B, 1C, 1D1, 1D2, 1E, 1F, 1G1, 1G2, 1H, 1I, 1J, 1K, 1L, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -2959,6 +3314,11 @@
           <t>92</t>
         </is>
       </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>1A1A, 1A1B, 1A2, 1B, 2A, 2B1A, 2B1B, 2B1C1, 2B1C2, 2B2, 2C1, 2C2</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -2966,6 +3326,11 @@
           <t>93</t>
         </is>
       </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -2973,6 +3338,11 @@
           <t>94</t>
         </is>
       </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>1A1A, 1A1A2, 1A2, 1A3, 1A4, 1A5, 1B, 1C, 1D, 1E, 2A, 2B, 3A, 3B, 4, 5A, 5B, 6, 7A, 7B, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -2980,6 +3350,11 @@
           <t>95</t>
         </is>
       </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 13, 14, 15, 16, 17, 2, 3, 4A1, 4A2, 4B, 4C1, 4C2, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -2987,6 +3362,11 @@
           <t>96</t>
         </is>
       </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -2994,6 +3374,11 @@
           <t>97</t>
         </is>
       </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>1, 10A1, 10A2, 10B1, 10B2, 11, 12, 13, 14, 15, 16, 17A, 17B, 2, 3, 4A, 4B, 4C, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -3001,11 +3386,21 @@
           <t>98</t>
         </is>
       </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
           <t>99</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
         </is>
       </c>
     </row>
